--- a/pm/HLW PM Mock Data.xlsx
+++ b/pm/HLW PM Mock Data.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Procurer</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -960,9 +960,6 @@
       <c r="C2" t="n">
         <v>900</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Hayden Harms</t>
@@ -983,9 +980,6 @@
       <c r="C3" t="n">
         <v>750</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Landon Lindsey</t>
@@ -1006,9 +1000,6 @@
       <c r="C4" t="n">
         <v>1600</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Landon Lindsey</t>
@@ -1044,7 +1035,6 @@
           <t>Hayden Harms</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1075,7 +1065,6 @@
           <t>Drew Wigley</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1106,7 +1095,6 @@
           <t>Hayden Harms</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pm/HLW PM Mock Data.xlsx
+++ b/pm/HLW PM Mock Data.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,90 +420,191 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cash On Hand</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Active Clients</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Entities</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A2" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B2" t="n">
+        <v>15200</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31200</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HLW Financial, LLC</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>46113</v>
       </c>
       <c r="B3" t="n">
+        <v>16100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4950</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11150</v>
+      </c>
+      <c r="E3" t="n">
+        <v>34500</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HLW Financial, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10700</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36700</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HLW Financial, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B5" t="n">
+        <v>17300</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E5" t="n">
+        <v>39100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HLW Financial, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B6" t="n">
+        <v>17950</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5150</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HLW Financial, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B7" t="n">
         <v>18400</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C7" t="n">
         <v>5250</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="D7" t="n">
         <v>13150</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cash On Hand</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="E7" t="n">
         <v>42300</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Active Clients</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="F7" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Entities</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>HLW Financial, LLC</t>
         </is>
@@ -517,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +650,11 @@
           <t>Partner</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -573,6 +682,9 @@
           <t>Hayden Harms</t>
         </is>
       </c>
+      <c r="F2" s="1" t="n">
+        <v>46237</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,6 +712,9 @@
           <t>Landon Lindsey</t>
         </is>
       </c>
+      <c r="F3" s="1" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,6 +742,9 @@
           <t>Drew Wigley</t>
         </is>
       </c>
+      <c r="F4" s="1" t="n">
+        <v>46225</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,6 +772,9 @@
           <t>Landon Lindsey</t>
         </is>
       </c>
+      <c r="F5" s="1" t="n">
+        <v>46238</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,6 +802,9 @@
           <t>Hayden Harms</t>
         </is>
       </c>
+      <c r="F6" s="1" t="n">
+        <v>46245</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -708,6 +832,9 @@
           <t>Drew Wigley</t>
         </is>
       </c>
+      <c r="F7" s="1" t="n">
+        <v>46213</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -735,6 +862,9 @@
           <t>Hayden Harms</t>
         </is>
       </c>
+      <c r="F8" s="1" t="n">
+        <v>46252</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,6 +891,249 @@
         <is>
           <t>Drew Wigley</t>
         </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ferris Family Dental</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Monthly Bookkeeping</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Overlook Ridge HOA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly Sales Tax</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Solano Import Co</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Advisory Retainer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kessler &amp; Vance Referral</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025 Individual Return</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Prepared</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hutto Family Trust</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025 Individual Return</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Copper Creek Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monthly Bookkeeping</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Docs Requested</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Alden Manufacturing LLC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Advisory Retainer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Priscilla Nguyen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025 Individual Return</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>E-Filed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46249</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +1161,11 @@
           <t>Hours Logged</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -796,7 +1174,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="3">
@@ -806,7 +1187,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="4">
@@ -816,7 +1200,88 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>9</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>46235</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +1410,11 @@
           <t>Bookkeeper</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -960,10 +1430,16 @@
       <c r="C2" t="n">
         <v>900</v>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Hayden Harms</t>
         </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>46237</v>
       </c>
     </row>
     <row r="3">
@@ -980,10 +1456,16 @@
       <c r="C3" t="n">
         <v>750</v>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Landon Lindsey</t>
         </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>46238</v>
       </c>
     </row>
     <row r="4">
@@ -1000,10 +1482,16 @@
       <c r="C4" t="n">
         <v>1600</v>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Landon Lindsey</t>
         </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>46239</v>
       </c>
     </row>
     <row r="5">
@@ -1035,6 +1523,10 @@
           <t>Hayden Harms</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="1" t="n">
+        <v>46254</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1065,6 +1557,10 @@
           <t>Drew Wigley</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="1" t="n">
+        <v>46245</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1094,6 +1590,190 @@
         <is>
           <t>Hayden Harms</t>
         </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="1" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ferris Family Dental</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bookkeeping</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Solano Import Co</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bookkeeping</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Copper Creek Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bookkeeping</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>640</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hutto Family Trust</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tax Prep</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>900</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="1" t="n">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kessler &amp; Vance Referral</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tax Prep</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" s="1" t="n">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Priscilla Nguyen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tax Prep</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>480</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Landon Lindsey</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Drew Wigley</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hayden Harms</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="1" t="n">
+        <v>46188</v>
       </c>
     </row>
   </sheetData>
